--- a/may_2026/output/tl4_tables.xlsx
+++ b/may_2026/output/tl4_tables.xlsx
@@ -1,799 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tulikajain/Documents/Veeraa/Pilot TL 4 5/analysis_may_26/output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DD3C47-E544-644E-A994-F54DBC0C2281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Active Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Impact Score" sheetId="2" r:id="rId2"/>
     <sheet name="Impact Areas" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="255">
-  <si>
-    <t>leader</t>
-  </si>
-  <si>
-    <t>active_comm</t>
-  </si>
-  <si>
-    <t>n_completed</t>
-  </si>
-  <si>
-    <t>n_dkleader</t>
-  </si>
-  <si>
-    <t>n_total</t>
-  </si>
-  <si>
-    <t>pct_active</t>
-  </si>
-  <si>
-    <t>leader_name</t>
-  </si>
-  <si>
-    <t>comm_size</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>total_active</t>
-  </si>
-  <si>
-    <t>ASJH</t>
-  </si>
-  <si>
-    <t>Augustina Soreng</t>
-  </si>
-  <si>
-    <t>15-05-2026</t>
-  </si>
-  <si>
-    <t>AYUP</t>
-  </si>
-  <si>
-    <t>Ajit Yadav</t>
-  </si>
-  <si>
-    <t>KMWB</t>
-  </si>
-  <si>
-    <t>Krishna Mondal</t>
-  </si>
-  <si>
-    <t>KPGJ</t>
-  </si>
-  <si>
-    <t>Khairun Pathan</t>
-  </si>
-  <si>
-    <t>SBUP</t>
-  </si>
-  <si>
-    <t>Shabnam Begum</t>
-  </si>
-  <si>
-    <t>SKDL</t>
-  </si>
-  <si>
-    <t>Suraj Kant</t>
-  </si>
-  <si>
-    <t>SSBH</t>
-  </si>
-  <si>
-    <t>Sanjay Sahni</t>
-  </si>
-  <si>
-    <t>Made worse</t>
-  </si>
-  <si>
-    <t>No impact</t>
-  </si>
-  <si>
-    <t>Some positive impact</t>
-  </si>
-  <si>
-    <t>Significantly improved</t>
-  </si>
-  <si>
-    <t>Saved life</t>
-  </si>
-  <si>
-    <t>Don't know/Don't remember</t>
-  </si>
-  <si>
-    <t>Survey left incomplete</t>
-  </si>
-  <si>
-    <t>total_positive</t>
-  </si>
-  <si>
-    <t>denom</t>
-  </si>
-  <si>
-    <t>pct_impact</t>
-  </si>
-  <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>label</t>
-  </si>
-  <si>
-    <t>...3</t>
-  </si>
-  <si>
-    <t>n_responders</t>
-  </si>
-  <si>
-    <t>impact_educ_1</t>
-  </si>
-  <si>
-    <t>Enrolled me in a government or private school</t>
-  </si>
-  <si>
-    <t>impact_educ_2</t>
-  </si>
-  <si>
-    <t>Gave me guidance on school/college admissions and studies</t>
-  </si>
-  <si>
-    <t>impact_educ_3</t>
-  </si>
-  <si>
-    <t>Helped me access scholarships</t>
-  </si>
-  <si>
-    <t>impact_educ_4</t>
-  </si>
-  <si>
-    <t>Conducted classes to improve learning levels</t>
-  </si>
-  <si>
-    <t>impact_educ_5</t>
-  </si>
-  <si>
-    <t>Provided vocational skills (including digital skills)</t>
-  </si>
-  <si>
-    <t>impact_educ_6</t>
-  </si>
-  <si>
-    <t>Linked to an existing skilling course</t>
-  </si>
-  <si>
-    <t>impact_educ_7</t>
-  </si>
-  <si>
-    <t>Provided training in sports and athletics</t>
-  </si>
-  <si>
-    <t>impact_educ_8</t>
-  </si>
-  <si>
-    <t>Provided soft/life skills: Creativity, leadership</t>
-  </si>
-  <si>
-    <t>impact_educ_9</t>
-  </si>
-  <si>
-    <t>Helped access other government education benefits (such as uniform, tablet, cycle, midday meal)</t>
-  </si>
-  <si>
-    <t>impact_educ_other</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>impact_aware_1</t>
-  </si>
-  <si>
-    <t>Protecting the environment</t>
-  </si>
-  <si>
-    <t>impact_aware_2</t>
-  </si>
-  <si>
-    <t>How to access government benefits</t>
-  </si>
-  <si>
-    <t>impact_aware_3</t>
-  </si>
-  <si>
-    <t>Gender norms</t>
-  </si>
-  <si>
-    <t>impact_aware_4</t>
-  </si>
-  <si>
-    <t>Sexual and reproductive health (including menstrual health)</t>
-  </si>
-  <si>
-    <t>impact_aware_5</t>
-  </si>
-  <si>
-    <t>Financial literacy (including cyber fraud) + entrepreneurship</t>
-  </si>
-  <si>
-    <t>impact_aware_6</t>
-  </si>
-  <si>
-    <t>My rights</t>
-  </si>
-  <si>
-    <t>impact_aware_7</t>
-  </si>
-  <si>
-    <t>Social norms: child marriage, caste/religious discrimination, dowry, domestic violence</t>
-  </si>
-  <si>
-    <t>impact_aware_8</t>
-  </si>
-  <si>
-    <t>Disease prevention and cure</t>
-  </si>
-  <si>
-    <t>impact_aware_9</t>
-  </si>
-  <si>
-    <t>Nutrition</t>
-  </si>
-  <si>
-    <t>impact_aware_10</t>
-  </si>
-  <si>
-    <t>Political participation</t>
-  </si>
-  <si>
-    <t>impact_aware_11</t>
-  </si>
-  <si>
-    <t>Agriculture/farming knowledge</t>
-  </si>
-  <si>
-    <t>impact_aware_other</t>
-  </si>
-  <si>
-    <t>impact_health_1</t>
-  </si>
-  <si>
-    <t>Got access to a government health scheme, entitlement, or worker (e.g. Ayushman Bharat, Janani Suraksha, ASHA worker)</t>
-  </si>
-  <si>
-    <t>impact_health_2</t>
-  </si>
-  <si>
-    <t>Got access to hospital, medicine, treatment, vaccination (government or private)</t>
-  </si>
-  <si>
-    <t>impact_health_3</t>
-  </si>
-  <si>
-    <t>Got support during a medical emergency (including teenage pregnancy)</t>
-  </si>
-  <si>
-    <t>impact_health_4</t>
-  </si>
-  <si>
-    <t>Got access to mental health support or counselling</t>
-  </si>
-  <si>
-    <t>impact_health_5</t>
-  </si>
-  <si>
-    <t>Improved sexual and reproductive health due to improved awareness</t>
-  </si>
-  <si>
-    <t>impact_health_6</t>
-  </si>
-  <si>
-    <t>Child's nutrition status improved due to improved awareness</t>
-  </si>
-  <si>
-    <t>impact_health_7</t>
-  </si>
-  <si>
-    <t>Reduced or stopped alcohol or drug use</t>
-  </si>
-  <si>
-    <t>impact_health_8</t>
-  </si>
-  <si>
-    <t>Got access to a disability benefits or equipment</t>
-  </si>
-  <si>
-    <t>impact_health_9</t>
-  </si>
-  <si>
-    <t>Less diseases and risks due to improved access to clean water</t>
-  </si>
-  <si>
-    <t>impact_health_10</t>
-  </si>
-  <si>
-    <t>Less diseases and risks due to improved access to clean air</t>
-  </si>
-  <si>
-    <t>impact_health_11</t>
-  </si>
-  <si>
-    <t>Improved health due to increased physical activity/sports</t>
-  </si>
-  <si>
-    <t>impact_health_other</t>
-  </si>
-  <si>
-    <t>impact_income_1</t>
-  </si>
-  <si>
-    <t>Got connected to a stable job (formal or informal)</t>
-  </si>
-  <si>
-    <t>impact_income_2</t>
-  </si>
-  <si>
-    <t>Started a business (myself or with others)</t>
-  </si>
-  <si>
-    <t>impact_income_3</t>
-  </si>
-  <si>
-    <t>Support a business venture started by others</t>
-  </si>
-  <si>
-    <t>impact_income_4</t>
-  </si>
-  <si>
-    <t>Got access to markets to sell produce or goods</t>
-  </si>
-  <si>
-    <t>impact_income_5</t>
-  </si>
-  <si>
-    <t>Got access to NREGA work and wages</t>
-  </si>
-  <si>
-    <t>impact_income_6</t>
-  </si>
-  <si>
-    <t>Started receiving a government pension (old age, disability, widow)</t>
-  </si>
-  <si>
-    <t>impact_income_7</t>
-  </si>
-  <si>
-    <t>Got access to a government livelihood scheme</t>
-  </si>
-  <si>
-    <t>impact_income_8</t>
-  </si>
-  <si>
-    <t>Got access to land and rights (e.g. forest rights) for cultivation/business</t>
-  </si>
-  <si>
-    <t>impact_income_9</t>
-  </si>
-  <si>
-    <t>Helped access a productive asset which supported livelihood (e.g. sewing machine)</t>
-  </si>
-  <si>
-    <t>impact_income_10</t>
-  </si>
-  <si>
-    <t>Improved productivity due to knowledge/inputs</t>
-  </si>
-  <si>
-    <t>impact_income_11</t>
-  </si>
-  <si>
-    <t>Save time due to water access, which I spend on income generating activities</t>
-  </si>
-  <si>
-    <t>impact_income_other</t>
-  </si>
-  <si>
-    <t>impact_finance_1</t>
-  </si>
-  <si>
-    <t>Opened a bank account</t>
-  </si>
-  <si>
-    <t>impact_finance_2</t>
-  </si>
-  <si>
-    <t>Started saving regularly (e.g. through an SHG or savings group)</t>
-  </si>
-  <si>
-    <t>impact_finance_3</t>
-  </si>
-  <si>
-    <t>Got access to private loan or credit</t>
-  </si>
-  <si>
-    <t>impact_finance_4</t>
-  </si>
-  <si>
-    <t>Got access to a government loan scheme (e.g. Mudra, PM SVANidhi)</t>
-  </si>
-  <si>
-    <t>impact_finance_5</t>
-  </si>
-  <si>
-    <t>Got help managing debt or repaying a loan</t>
-  </si>
-  <si>
-    <t>impact_finance_6</t>
-  </si>
-  <si>
-    <t>Got access to insurance</t>
-  </si>
-  <si>
-    <t>impact_finance_other</t>
-  </si>
-  <si>
-    <t>impact_harm_1</t>
-  </si>
-  <si>
-    <t>Protected from or supported through domestic violence</t>
-  </si>
-  <si>
-    <t>impact_harm_2</t>
-  </si>
-  <si>
-    <t>Protected from or supported through sexual harassment or assault</t>
-  </si>
-  <si>
-    <t>impact_harm_3</t>
-  </si>
-  <si>
-    <t>Prevented or escaped a forced or child marriage</t>
-  </si>
-  <si>
-    <t>impact_harm_4</t>
-  </si>
-  <si>
-    <t>Protected from or supported through dowry harassment</t>
-  </si>
-  <si>
-    <t>impact_harm_5</t>
-  </si>
-  <si>
-    <t>Rescued from or prevented trafficking</t>
-  </si>
-  <si>
-    <t>impact_harm_6</t>
-  </si>
-  <si>
-    <t>Protected from caste-based violence or discrimination</t>
-  </si>
-  <si>
-    <t>impact_harm_7</t>
-  </si>
-  <si>
-    <t>Protected from religious discrimination or communal violence</t>
-  </si>
-  <si>
-    <t>impact_harm_8</t>
-  </si>
-  <si>
-    <t>Supported to file a police complaint or FIR for a minor offence</t>
-  </si>
-  <si>
-    <t>impact_harm_9</t>
-  </si>
-  <si>
-    <t>Supported to file a police complaint or FIR for a major offence</t>
-  </si>
-  <si>
-    <t>impact_harm_10</t>
-  </si>
-  <si>
-    <t>Got access to a shelter or safe house</t>
-  </si>
-  <si>
-    <t>impact_harm_11</t>
-  </si>
-  <si>
-    <t>Received compensation as a survivor of violence or crime</t>
-  </si>
-  <si>
-    <t>impact_harm_12</t>
-  </si>
-  <si>
-    <t>A public space that felt unsafe has been made safer</t>
-  </si>
-  <si>
-    <t>impact_harm_13</t>
-  </si>
-  <si>
-    <t>Protected from exploitation by an employer or contractor</t>
-  </si>
-  <si>
-    <t>impact_harm_14</t>
-  </si>
-  <si>
-    <t>Protected and supported in a case of witchcraft</t>
-  </si>
-  <si>
-    <t>impact_harm_other</t>
-  </si>
-  <si>
-    <t>impact_confidence_1</t>
-  </si>
-  <si>
-    <t>I no longer wear a ghungat/wear it less</t>
-  </si>
-  <si>
-    <t>impact_confidence_2</t>
-  </si>
-  <si>
-    <t>I have improved mobility (e.g., can go outside the house more often)</t>
-  </si>
-  <si>
-    <t>impact_confidence_3</t>
-  </si>
-  <si>
-    <t>Improved decisionmaking (can say "no", can weigh in on decisions)</t>
-  </si>
-  <si>
-    <t>impact_confidence_4</t>
-  </si>
-  <si>
-    <t>I speak up more often (in the house, in meetings)</t>
-  </si>
-  <si>
-    <t>impact_confidence_5</t>
-  </si>
-  <si>
-    <t>Improved leadership skills (eg public speaking, have taken a leadership role)</t>
-  </si>
-  <si>
-    <t>impact_confidence_6</t>
-  </si>
-  <si>
-    <t>I feel more respected by my family/peers</t>
-  </si>
-  <si>
-    <t>impact_confidence_7</t>
-  </si>
-  <si>
-    <t>I no longer feel ashamed about my caste, religion or identity</t>
-  </si>
-  <si>
-    <t>impact_confidence_8</t>
-  </si>
-  <si>
-    <t>I am more likely to participate in public events</t>
-  </si>
-  <si>
-    <t>impact_confidence_other</t>
-  </si>
-  <si>
-    <t>impact_govt_access_1</t>
-  </si>
-  <si>
-    <t>Helped with government documents (e.g. Aadhar, ration card, birth certificate, caste certificate)</t>
-  </si>
-  <si>
-    <t>impact_govt_access_2</t>
-  </si>
-  <si>
-    <t>Helped with PM Awaas application</t>
-  </si>
-  <si>
-    <t>impact_govt_access_3</t>
-  </si>
-  <si>
-    <t>Helped access Swach Bharat toilet</t>
-  </si>
-  <si>
-    <t>impact_govt_access_4</t>
-  </si>
-  <si>
-    <t>Helped access food entitlements (e.g. ration card, PDS access)</t>
-  </si>
-  <si>
-    <t>impact_govt_access_5</t>
-  </si>
-  <si>
-    <t>Helped with road application</t>
-  </si>
-  <si>
-    <t>impact_govt_access_6</t>
-  </si>
-  <si>
-    <t>Got support navigating the police, courts, or legal system</t>
-  </si>
-  <si>
-    <t>impact_govt_access_7</t>
-  </si>
-  <si>
-    <t>Won a legal case or received a legal judgment in our favour</t>
-  </si>
-  <si>
-    <t>impact_govt_access_8</t>
-  </si>
-  <si>
-    <t>Filed an RTI and/or received a response</t>
-  </si>
-  <si>
-    <t>impact_govt_access_other</t>
-  </si>
-  <si>
-    <t>impact_water_land_1</t>
-  </si>
-  <si>
-    <t>Got access to clean drinking water that was not available before</t>
-  </si>
-  <si>
-    <t>impact_water_land_2</t>
-  </si>
-  <si>
-    <t>Distance to water source has reduced</t>
-  </si>
-  <si>
-    <t>impact_water_land_3</t>
-  </si>
-  <si>
-    <t>Got access to water for farming or for household needs</t>
-  </si>
-  <si>
-    <t>impact_water_land_4</t>
-  </si>
-  <si>
-    <t>Got access to land as compensation</t>
-  </si>
-  <si>
-    <t>impact_water_land_5</t>
-  </si>
-  <si>
-    <t>Got forest land or produce rights (e.g. NTFP, Forest Rights Act patta)</t>
-  </si>
-  <si>
-    <t>impact_water_land_6</t>
-  </si>
-  <si>
-    <t>Prevented illegal occupation or grabbing of land</t>
-  </si>
-  <si>
-    <t>impact_water_land_7</t>
-  </si>
-  <si>
-    <t>Got a land title or ownership document made or corrected</t>
-  </si>
-  <si>
-    <t>impact_water_land_8</t>
-  </si>
-  <si>
-    <t>Got access to common land that was previously blocked</t>
-  </si>
-  <si>
-    <t>impact_water_land_other</t>
-  </si>
-  <si>
-    <t>impact_belong_1</t>
-  </si>
-  <si>
-    <t>Feel less alone or isolated than before (have made new friends)</t>
-  </si>
-  <si>
-    <t>impact_belong_2</t>
-  </si>
-  <si>
-    <t>Feel that people in my community look out for each other</t>
-  </si>
-  <si>
-    <t>impact_belong_3</t>
-  </si>
-  <si>
-    <t>Feel that I belong to a group that shares my struggles and values</t>
-  </si>
-  <si>
-    <t>impact_belong_4</t>
-  </si>
-  <si>
-    <t>Feel more hopeful about the future because of the people around me</t>
-  </si>
-  <si>
-    <t>impact_belong_5</t>
-  </si>
-  <si>
-    <t>Conflict or tension within the community has reduced</t>
-  </si>
-  <si>
-    <t>impact_belong_6</t>
-  </si>
-  <si>
-    <t>People from different castes, religions, or backgrounds are mixing more than before</t>
-  </si>
-  <si>
-    <t>impact_belong_other</t>
-  </si>
-  <si>
-    <t>impact_envir_1</t>
-  </si>
-  <si>
-    <t>Participated in tree planting or forest conservation</t>
-  </si>
-  <si>
-    <t>impact_envir_2</t>
-  </si>
-  <si>
-    <t>Helped protect a water body (e.g. river, pond, wetland)</t>
-  </si>
-  <si>
-    <t>impact_envir_3</t>
-  </si>
-  <si>
-    <t>Reduced use of chemical fertilisers or pesticides in farming</t>
-  </si>
-  <si>
-    <t>impact_envir_4</t>
-  </si>
-  <si>
-    <t>Adopted climate-resilient farming practices</t>
-  </si>
-  <si>
-    <t>impact_envir_5</t>
-  </si>
-  <si>
-    <t>Protected common land or forest from encroachment or destruction</t>
-  </si>
-  <si>
-    <t>impact_envir_6</t>
-  </si>
-  <si>
-    <t>Community is better prepared for floods, droughts, heatwaves, other natural disasters</t>
-  </si>
-  <si>
-    <t>impact_envir_7</t>
-  </si>
-  <si>
-    <t>Got support during or after a natural disaster</t>
-  </si>
-  <si>
-    <t>impact_envir_8</t>
-  </si>
-  <si>
-    <t>Waste management in the village or neighbourhood has improved</t>
-  </si>
-  <si>
-    <t>impact_envir_9</t>
-  </si>
-  <si>
-    <t>Air or water pollution in the area has reduced</t>
-  </si>
-  <si>
-    <t>impact_envir_10</t>
-  </si>
-  <si>
-    <t>Feel better prepared for the climate crisis and its impact on future generations</t>
-  </si>
-  <si>
-    <t>impact_envir_other</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -841,21 +65,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -893,7 +109,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -927,7 +143,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -962,10 +177,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1138,53 +352,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="4" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.1640625" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>10</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>leader</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>active_comm</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_completed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_dkleader</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>n_total</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pct_active</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>leader_name</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>comm_size</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ASJH</t>
+        </is>
       </c>
       <c r="B2">
         <v>80</v>
@@ -1201,22 +429,28 @@
       <c r="F2">
         <v>85.11</v>
       </c>
-      <c r="G2" t="s">
-        <v>11</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Augustina Soreng</t>
+        </is>
       </c>
       <c r="H2">
         <v>921</v>
       </c>
-      <c r="I2" t="s">
-        <v>12</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
       </c>
       <c r="J2">
-        <v>783.86309999999992</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>13</v>
+        <v>783.8630999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AYUP</t>
+        </is>
       </c>
       <c r="B3">
         <v>33</v>
@@ -1233,22 +467,28 @@
       <c r="F3">
         <v>97.06</v>
       </c>
-      <c r="G3" t="s">
-        <v>14</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ajit Yadav</t>
+        </is>
       </c>
       <c r="H3">
         <v>50</v>
       </c>
-      <c r="I3" t="s">
-        <v>12</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
       </c>
       <c r="J3">
         <v>48.53</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KMWB</t>
+        </is>
       </c>
       <c r="B4">
         <v>18</v>
@@ -1263,24 +503,30 @@
         <v>19</v>
       </c>
       <c r="F4">
-        <v>94.74</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Krishna Mondal</t>
+        </is>
       </c>
       <c r="H4">
         <v>33</v>
       </c>
-      <c r="I4" t="s">
-        <v>12</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
       </c>
       <c r="J4">
-        <v>31.264199999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>17</v>
+        <v>31.2642</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KPGJ</t>
+        </is>
       </c>
       <c r="B5">
         <v>46</v>
@@ -1297,22 +543,28 @@
       <c r="F5">
         <v>90.2</v>
       </c>
-      <c r="G5" t="s">
-        <v>18</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Khairun Pathan</t>
+        </is>
       </c>
       <c r="H5">
         <v>95</v>
       </c>
-      <c r="I5" t="s">
-        <v>12</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
       </c>
       <c r="J5">
         <v>85.69</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>19</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SBUP</t>
+        </is>
       </c>
       <c r="B6">
         <v>71</v>
@@ -1329,22 +581,28 @@
       <c r="F6">
         <v>98.61</v>
       </c>
-      <c r="G6" t="s">
-        <v>20</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Shabnam Begum</t>
+        </is>
       </c>
       <c r="H6">
         <v>146</v>
       </c>
-      <c r="I6" t="s">
-        <v>12</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
       </c>
       <c r="J6">
-        <v>143.97059999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>143.9706</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SKDL</t>
+        </is>
       </c>
       <c r="B7">
         <v>83</v>
@@ -1361,22 +619,28 @@
       <c r="F7">
         <v>98.81</v>
       </c>
-      <c r="G7" t="s">
-        <v>22</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Suraj Kant</t>
+        </is>
       </c>
       <c r="H7">
         <v>471</v>
       </c>
-      <c r="I7" t="s">
-        <v>12</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
       </c>
       <c r="J7">
-        <v>465.39510000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>465.3951</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSBH</t>
+        </is>
       </c>
       <c r="B8">
         <v>82</v>
@@ -1393,17 +657,21 @@
       <c r="F8">
         <v>96.47</v>
       </c>
-      <c r="G8" t="s">
-        <v>24</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sanjay Sahni</t>
+        </is>
       </c>
       <c r="H8">
         <v>415</v>
       </c>
-      <c r="I8" t="s">
-        <v>12</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15-05-2026</t>
+        </is>
       </c>
       <c r="J8">
-        <v>400.35050000000001</v>
+        <v>400.3505</v>
       </c>
     </row>
   </sheetData>
@@ -1412,54 +680,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>leader</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>leader_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Made worse</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>No impact</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Some positive impact</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Significantly improved</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Saved life</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Don't know/Don't remember</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Survey left incomplete</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>total_positive</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>denom</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>pct_impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AYUP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ajit Yadav</t>
+        </is>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1492,12 +788,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KMWB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Krishna Mondal</t>
+        </is>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1530,12 +830,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SKDL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Suraj Kant</t>
+        </is>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1568,12 +872,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ASJH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Augustina Soreng</t>
+        </is>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1606,12 +914,16 @@
         <v>97.33</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSBH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sanjay Sahni</t>
+        </is>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1644,12 +956,16 @@
         <v>94.87</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SBUP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Shabnam Begum</t>
+        </is>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1682,12 +998,16 @@
         <v>92.75</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KPGJ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Khairun Pathan</t>
+        </is>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1726,45 +1046,67 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>38</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ASJH</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AYUP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>KMWB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>KPGJ</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SBUP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SKDL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SSBH</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>n_responders</t>
+        </is>
       </c>
       <c r="B2">
         <v>78</v>
@@ -1788,9 +1130,11 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>39</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>impact_educ_1</t>
+        </is>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1813,13 +1157,17 @@
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>41</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Enrolled me in a government or private school</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>impact_educ_2</t>
+        </is>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1842,13 +1190,17 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>43</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Gave me guidance on school/college admissions and studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>impact_educ_3</t>
+        </is>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1871,13 +1223,17 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>45</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Helped me access scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>impact_educ_4</t>
+        </is>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1900,13 +1256,17 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>47</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Conducted classes to improve learning levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>impact_educ_5</t>
+        </is>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1929,13 +1289,17 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>49</v>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Provided vocational skills (including digital skills)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>impact_educ_6</t>
+        </is>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1958,13 +1322,17 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>51</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Linked to an existing skilling course</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>impact_educ_7</t>
+        </is>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1987,13 +1355,17 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>53</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Provided training in sports and athletics</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>impact_educ_8</t>
+        </is>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2016,13 +1388,17 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>55</v>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Provided soft/life skills: Creativity, leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>impact_educ_9</t>
+        </is>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2045,13 +1421,17 @@
       <c r="H11">
         <v>1</v>
       </c>
-      <c r="I11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>57</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Helped access other government education benefits (such as uniform, tablet, cycle, midday meal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>impact_educ_other</t>
+        </is>
       </c>
       <c r="B12">
         <v>2</v>
@@ -2074,13 +1454,17 @@
       <c r="H12">
         <v>1</v>
       </c>
-      <c r="I12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>59</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>impact_aware_1</t>
+        </is>
       </c>
       <c r="B13">
         <v>31</v>
@@ -2103,13 +1487,17 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>61</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Protecting the environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>impact_aware_2</t>
+        </is>
       </c>
       <c r="B14">
         <v>26</v>
@@ -2132,13 +1520,17 @@
       <c r="H14">
         <v>10</v>
       </c>
-      <c r="I14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>63</v>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>How to access government benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>impact_aware_3</t>
+        </is>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2161,13 +1553,17 @@
       <c r="H15">
         <v>2</v>
       </c>
-      <c r="I15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>65</v>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Gender norms</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>impact_aware_4</t>
+        </is>
       </c>
       <c r="B16">
         <v>8</v>
@@ -2190,13 +1586,17 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>67</v>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sexual and reproductive health (including menstrual health)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>impact_aware_5</t>
+        </is>
       </c>
       <c r="B17">
         <v>31</v>
@@ -2219,13 +1619,17 @@
       <c r="H17">
         <v>2</v>
       </c>
-      <c r="I17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>69</v>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Financial literacy (including cyber fraud) + entrepreneurship</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>impact_aware_6</t>
+        </is>
       </c>
       <c r="B18">
         <v>7</v>
@@ -2248,13 +1652,17 @@
       <c r="H18">
         <v>1</v>
       </c>
-      <c r="I18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>71</v>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>My rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>impact_aware_7</t>
+        </is>
       </c>
       <c r="B19">
         <v>4</v>
@@ -2277,13 +1685,17 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>73</v>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Social norms: child marriage, caste/religious discrimination, dowry, domestic violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>impact_aware_8</t>
+        </is>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2306,13 +1718,17 @@
       <c r="H20">
         <v>1</v>
       </c>
-      <c r="I20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>75</v>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Disease prevention and cure</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>impact_aware_9</t>
+        </is>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2335,13 +1751,17 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>77</v>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>impact_aware_10</t>
+        </is>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2364,13 +1784,17 @@
       <c r="H22">
         <v>0</v>
       </c>
-      <c r="I22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>79</v>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Political participation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>impact_aware_11</t>
+        </is>
       </c>
       <c r="B23">
         <v>7</v>
@@ -2393,13 +1817,17 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>81</v>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Agriculture/farming knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>impact_aware_other</t>
+        </is>
       </c>
       <c r="B24">
         <v>4</v>
@@ -2422,13 +1850,17 @@
       <c r="H24">
         <v>2</v>
       </c>
-      <c r="I24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>82</v>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>impact_health_1</t>
+        </is>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2451,13 +1883,17 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>84</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Got access to a government health scheme, entitlement, or worker (e.g. Ayushman Bharat, Janani Suraksha, ASHA worker)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>impact_health_2</t>
+        </is>
       </c>
       <c r="B26">
         <v>3</v>
@@ -2480,13 +1916,17 @@
       <c r="H26">
         <v>0</v>
       </c>
-      <c r="I26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>86</v>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Got access to hospital, medicine, treatment, vaccination (government or private)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>impact_health_3</t>
+        </is>
       </c>
       <c r="B27">
         <v>1</v>
@@ -2509,13 +1949,17 @@
       <c r="H27">
         <v>1</v>
       </c>
-      <c r="I27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>88</v>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Got support during a medical emergency (including teenage pregnancy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>impact_health_4</t>
+        </is>
       </c>
       <c r="B28">
         <v>1</v>
@@ -2538,13 +1982,17 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>90</v>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Got access to mental health support or counselling</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>impact_health_5</t>
+        </is>
       </c>
       <c r="B29">
         <v>1</v>
@@ -2567,13 +2015,17 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>92</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Improved sexual and reproductive health due to improved awareness</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>impact_health_6</t>
+        </is>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2596,13 +2048,17 @@
       <c r="H30">
         <v>0</v>
       </c>
-      <c r="I30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>94</v>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Child's nutrition status improved due to improved awareness</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>impact_health_7</t>
+        </is>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2625,13 +2081,17 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>96</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Reduced or stopped alcohol or drug use</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>impact_health_8</t>
+        </is>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2654,13 +2114,17 @@
       <c r="H32">
         <v>0</v>
       </c>
-      <c r="I32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>98</v>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Got access to a disability benefits or equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>impact_health_9</t>
+        </is>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2683,13 +2147,17 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>100</v>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Less diseases and risks due to improved access to clean water</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>impact_health_10</t>
+        </is>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2712,13 +2180,17 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>102</v>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Less diseases and risks due to improved access to clean air</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>impact_health_11</t>
+        </is>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2741,13 +2213,17 @@
       <c r="H35">
         <v>0</v>
       </c>
-      <c r="I35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>104</v>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Improved health due to increased physical activity/sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>impact_health_other</t>
+        </is>
       </c>
       <c r="B36">
         <v>10</v>
@@ -2770,13 +2246,17 @@
       <c r="H36">
         <v>3</v>
       </c>
-      <c r="I36" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>105</v>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>impact_income_1</t>
+        </is>
       </c>
       <c r="B37">
         <v>8</v>
@@ -2799,13 +2279,17 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>107</v>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Got connected to a stable job (formal or informal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>impact_income_2</t>
+        </is>
       </c>
       <c r="B38">
         <v>14</v>
@@ -2828,13 +2312,17 @@
       <c r="H38">
         <v>0</v>
       </c>
-      <c r="I38" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>109</v>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Started a business (myself or with others)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>impact_income_3</t>
+        </is>
       </c>
       <c r="B39">
         <v>17</v>
@@ -2857,13 +2345,17 @@
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>111</v>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Support a business venture started by others</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>impact_income_4</t>
+        </is>
       </c>
       <c r="B40">
         <v>32</v>
@@ -2886,13 +2378,17 @@
       <c r="H40">
         <v>0</v>
       </c>
-      <c r="I40" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>113</v>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Got access to markets to sell produce or goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>impact_income_5</t>
+        </is>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2915,13 +2411,17 @@
       <c r="H41">
         <v>72</v>
       </c>
-      <c r="I41" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>115</v>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Got access to NREGA work and wages</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>impact_income_6</t>
+        </is>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2944,13 +2444,17 @@
       <c r="H42">
         <v>2</v>
       </c>
-      <c r="I42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>117</v>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Started receiving a government pension (old age, disability, widow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>impact_income_7</t>
+        </is>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2973,13 +2477,17 @@
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>119</v>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Got access to a government livelihood scheme</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>impact_income_8</t>
+        </is>
       </c>
       <c r="B44">
         <v>2</v>
@@ -3002,13 +2510,17 @@
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>121</v>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Got access to land and rights (e.g. forest rights) for cultivation/business</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>impact_income_9</t>
+        </is>
       </c>
       <c r="B45">
         <v>1</v>
@@ -3031,13 +2543,17 @@
       <c r="H45">
         <v>0</v>
       </c>
-      <c r="I45" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>123</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Helped access a productive asset which supported livelihood (e.g. sewing machine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>impact_income_10</t>
+        </is>
       </c>
       <c r="B46">
         <v>7</v>
@@ -3060,13 +2576,17 @@
       <c r="H46">
         <v>0</v>
       </c>
-      <c r="I46" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>125</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Improved productivity due to knowledge/inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>impact_income_11</t>
+        </is>
       </c>
       <c r="B47">
         <v>0</v>
@@ -3089,13 +2609,17 @@
       <c r="H47">
         <v>3</v>
       </c>
-      <c r="I47" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>127</v>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Save time due to water access, which I spend on income generating activities</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>impact_income_other</t>
+        </is>
       </c>
       <c r="B48">
         <v>6</v>
@@ -3118,13 +2642,17 @@
       <c r="H48">
         <v>1</v>
       </c>
-      <c r="I48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>128</v>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>impact_finance_1</t>
+        </is>
       </c>
       <c r="B49">
         <v>1</v>
@@ -3147,13 +2675,17 @@
       <c r="H49">
         <v>0</v>
       </c>
-      <c r="I49" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>130</v>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Opened a bank account</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>impact_finance_2</t>
+        </is>
       </c>
       <c r="B50">
         <v>0</v>
@@ -3176,13 +2708,17 @@
       <c r="H50">
         <v>5</v>
       </c>
-      <c r="I50" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>132</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Started saving regularly (e.g. through an SHG or savings group)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>impact_finance_3</t>
+        </is>
       </c>
       <c r="B51">
         <v>0</v>
@@ -3205,13 +2741,17 @@
       <c r="H51">
         <v>0</v>
       </c>
-      <c r="I51" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>134</v>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Got access to private loan or credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>impact_finance_4</t>
+        </is>
       </c>
       <c r="B52">
         <v>0</v>
@@ -3234,13 +2774,17 @@
       <c r="H52">
         <v>4</v>
       </c>
-      <c r="I52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>136</v>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Got access to a government loan scheme (e.g. Mudra, PM SVANidhi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>impact_finance_5</t>
+        </is>
       </c>
       <c r="B53">
         <v>0</v>
@@ -3263,13 +2807,17 @@
       <c r="H53">
         <v>0</v>
       </c>
-      <c r="I53" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>138</v>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Got help managing debt or repaying a loan</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>impact_finance_6</t>
+        </is>
       </c>
       <c r="B54">
         <v>0</v>
@@ -3292,13 +2840,17 @@
       <c r="H54">
         <v>1</v>
       </c>
-      <c r="I54" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>140</v>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Got access to insurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>impact_finance_other</t>
+        </is>
       </c>
       <c r="B55">
         <v>2</v>
@@ -3321,13 +2873,17 @@
       <c r="H55">
         <v>0</v>
       </c>
-      <c r="I55" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>141</v>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>impact_harm_1</t>
+        </is>
       </c>
       <c r="B56">
         <v>1</v>
@@ -3350,13 +2906,17 @@
       <c r="H56">
         <v>0</v>
       </c>
-      <c r="I56" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>143</v>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Protected from or supported through domestic violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>impact_harm_2</t>
+        </is>
       </c>
       <c r="B57">
         <v>0</v>
@@ -3379,13 +2939,17 @@
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>145</v>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Protected from or supported through sexual harassment or assault</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>impact_harm_3</t>
+        </is>
       </c>
       <c r="B58">
         <v>0</v>
@@ -3408,13 +2972,17 @@
       <c r="H58">
         <v>0</v>
       </c>
-      <c r="I58" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>147</v>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Prevented or escaped a forced or child marriage</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>impact_harm_4</t>
+        </is>
       </c>
       <c r="B59">
         <v>0</v>
@@ -3437,13 +3005,17 @@
       <c r="H59">
         <v>0</v>
       </c>
-      <c r="I59" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>149</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Protected from or supported through dowry harassment</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>impact_harm_5</t>
+        </is>
       </c>
       <c r="B60">
         <v>0</v>
@@ -3466,13 +3038,17 @@
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>151</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Rescued from or prevented trafficking</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>impact_harm_6</t>
+        </is>
       </c>
       <c r="B61">
         <v>0</v>
@@ -3495,13 +3071,17 @@
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>153</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Protected from caste-based violence or discrimination</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>impact_harm_7</t>
+        </is>
       </c>
       <c r="B62">
         <v>0</v>
@@ -3524,13 +3104,17 @@
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>155</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Protected from religious discrimination or communal violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>impact_harm_8</t>
+        </is>
       </c>
       <c r="B63">
         <v>0</v>
@@ -3553,13 +3137,17 @@
       <c r="H63">
         <v>0</v>
       </c>
-      <c r="I63" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>157</v>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Supported to file a police complaint or FIR for a minor offence</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>impact_harm_9</t>
+        </is>
       </c>
       <c r="B64">
         <v>2</v>
@@ -3582,13 +3170,17 @@
       <c r="H64">
         <v>0</v>
       </c>
-      <c r="I64" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>159</v>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Supported to file a police complaint or FIR for a major offence</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>impact_harm_10</t>
+        </is>
       </c>
       <c r="B65">
         <v>0</v>
@@ -3611,13 +3203,17 @@
       <c r="H65">
         <v>0</v>
       </c>
-      <c r="I65" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>161</v>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Got access to a shelter or safe house</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>impact_harm_11</t>
+        </is>
       </c>
       <c r="B66">
         <v>0</v>
@@ -3640,13 +3236,17 @@
       <c r="H66">
         <v>0</v>
       </c>
-      <c r="I66" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>163</v>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Received compensation as a survivor of violence or crime</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>impact_harm_12</t>
+        </is>
       </c>
       <c r="B67">
         <v>0</v>
@@ -3669,13 +3269,17 @@
       <c r="H67">
         <v>0</v>
       </c>
-      <c r="I67" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>165</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>A public space that felt unsafe has been made safer</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>impact_harm_13</t>
+        </is>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3698,13 +3302,17 @@
       <c r="H68">
         <v>0</v>
       </c>
-      <c r="I68" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>167</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Protected from exploitation by an employer or contractor</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>impact_harm_14</t>
+        </is>
       </c>
       <c r="B69">
         <v>0</v>
@@ -3727,13 +3335,17 @@
       <c r="H69">
         <v>0</v>
       </c>
-      <c r="I69" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>169</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Protected and supported in a case of witchcraft</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>impact_harm_other</t>
+        </is>
       </c>
       <c r="B70">
         <v>2</v>
@@ -3756,13 +3368,17 @@
       <c r="H70">
         <v>0</v>
       </c>
-      <c r="I70" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>170</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>impact_confidence_1</t>
+        </is>
       </c>
       <c r="B71">
         <v>0</v>
@@ -3785,13 +3401,17 @@
       <c r="H71">
         <v>0</v>
       </c>
-      <c r="I71" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>172</v>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>I no longer wear a ghungat/wear it less</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>impact_confidence_2</t>
+        </is>
       </c>
       <c r="B72">
         <v>6</v>
@@ -3814,13 +3434,17 @@
       <c r="H72">
         <v>2</v>
       </c>
-      <c r="I72" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>174</v>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>I have improved mobility (e.g., can go outside the house more often)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>impact_confidence_3</t>
+        </is>
       </c>
       <c r="B73">
         <v>16</v>
@@ -3843,13 +3467,17 @@
       <c r="H73">
         <v>0</v>
       </c>
-      <c r="I73" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>176</v>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Improved decisionmaking (can say "no", can weigh in on decisions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>impact_confidence_4</t>
+        </is>
       </c>
       <c r="B74">
         <v>8</v>
@@ -3872,13 +3500,17 @@
       <c r="H74">
         <v>0</v>
       </c>
-      <c r="I74" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>178</v>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>I speak up more often (in the house, in meetings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>impact_confidence_5</t>
+        </is>
       </c>
       <c r="B75">
         <v>7</v>
@@ -3901,13 +3533,17 @@
       <c r="H75">
         <v>0</v>
       </c>
-      <c r="I75" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>180</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Improved leadership skills (eg public speaking, have taken a leadership role)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>impact_confidence_6</t>
+        </is>
       </c>
       <c r="B76">
         <v>6</v>
@@ -3930,13 +3566,17 @@
       <c r="H76">
         <v>0</v>
       </c>
-      <c r="I76" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>182</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>I feel more respected by my family/peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>impact_confidence_7</t>
+        </is>
       </c>
       <c r="B77">
         <v>0</v>
@@ -3959,13 +3599,17 @@
       <c r="H77">
         <v>0</v>
       </c>
-      <c r="I77" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>184</v>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>I no longer feel ashamed about my caste, religion or identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>impact_confidence_8</t>
+        </is>
       </c>
       <c r="B78">
         <v>15</v>
@@ -3988,13 +3632,17 @@
       <c r="H78">
         <v>1</v>
       </c>
-      <c r="I78" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>186</v>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>I am more likely to participate in public events</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>impact_confidence_other</t>
+        </is>
       </c>
       <c r="B79">
         <v>0</v>
@@ -4017,13 +3665,17 @@
       <c r="H79">
         <v>0</v>
       </c>
-      <c r="I79" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>187</v>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>impact_govt_access_1</t>
+        </is>
       </c>
       <c r="B80">
         <v>0</v>
@@ -4046,13 +3698,17 @@
       <c r="H80">
         <v>1</v>
       </c>
-      <c r="I80" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>189</v>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Helped with government documents (e.g. Aadhar, ration card, birth certificate, caste certificate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>impact_govt_access_2</t>
+        </is>
       </c>
       <c r="B81">
         <v>1</v>
@@ -4075,13 +3731,17 @@
       <c r="H81">
         <v>1</v>
       </c>
-      <c r="I81" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>191</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Helped with PM Awaas application</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>impact_govt_access_3</t>
+        </is>
       </c>
       <c r="B82">
         <v>0</v>
@@ -4104,13 +3764,17 @@
       <c r="H82">
         <v>0</v>
       </c>
-      <c r="I82" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>193</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Helped access Swach Bharat toilet</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>impact_govt_access_4</t>
+        </is>
       </c>
       <c r="B83">
         <v>0</v>
@@ -4133,13 +3797,17 @@
       <c r="H83">
         <v>1</v>
       </c>
-      <c r="I83" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>195</v>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Helped access food entitlements (e.g. ration card, PDS access)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>impact_govt_access_5</t>
+        </is>
       </c>
       <c r="B84">
         <v>0</v>
@@ -4162,13 +3830,17 @@
       <c r="H84">
         <v>1</v>
       </c>
-      <c r="I84" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>197</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Helped with road application</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>impact_govt_access_6</t>
+        </is>
       </c>
       <c r="B85">
         <v>4</v>
@@ -4191,13 +3863,17 @@
       <c r="H85">
         <v>0</v>
       </c>
-      <c r="I85" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>199</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Got support navigating the police, courts, or legal system</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>impact_govt_access_7</t>
+        </is>
       </c>
       <c r="B86">
         <v>0</v>
@@ -4220,13 +3896,17 @@
       <c r="H86">
         <v>0</v>
       </c>
-      <c r="I86" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>201</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Won a legal case or received a legal judgment in our favour</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>impact_govt_access_8</t>
+        </is>
       </c>
       <c r="B87">
         <v>0</v>
@@ -4249,13 +3929,17 @@
       <c r="H87">
         <v>0</v>
       </c>
-      <c r="I87" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>203</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Filed an RTI and/or received a response</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>impact_govt_access_other</t>
+        </is>
       </c>
       <c r="B88">
         <v>2</v>
@@ -4278,13 +3962,17 @@
       <c r="H88">
         <v>2</v>
       </c>
-      <c r="I88" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>204</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>impact_water_land_1</t>
+        </is>
       </c>
       <c r="B89">
         <v>0</v>
@@ -4307,13 +3995,17 @@
       <c r="H89">
         <v>3</v>
       </c>
-      <c r="I89" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>206</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Got access to clean drinking water that was not available before</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>impact_water_land_2</t>
+        </is>
       </c>
       <c r="B90">
         <v>0</v>
@@ -4336,13 +4028,17 @@
       <c r="H90">
         <v>1</v>
       </c>
-      <c r="I90" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>208</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Distance to water source has reduced</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>impact_water_land_3</t>
+        </is>
       </c>
       <c r="B91">
         <v>0</v>
@@ -4365,13 +4061,17 @@
       <c r="H91">
         <v>0</v>
       </c>
-      <c r="I91" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>210</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Got access to water for farming or for household needs</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>impact_water_land_4</t>
+        </is>
       </c>
       <c r="B92">
         <v>0</v>
@@ -4394,13 +4094,17 @@
       <c r="H92">
         <v>0</v>
       </c>
-      <c r="I92" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>212</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Got access to land as compensation</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>impact_water_land_5</t>
+        </is>
       </c>
       <c r="B93">
         <v>2</v>
@@ -4423,13 +4127,17 @@
       <c r="H93">
         <v>0</v>
       </c>
-      <c r="I93" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>214</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Got forest land or produce rights (e.g. NTFP, Forest Rights Act patta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>impact_water_land_6</t>
+        </is>
       </c>
       <c r="B94">
         <v>1</v>
@@ -4452,13 +4160,17 @@
       <c r="H94">
         <v>0</v>
       </c>
-      <c r="I94" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>216</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Prevented illegal occupation or grabbing of land</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>impact_water_land_7</t>
+        </is>
       </c>
       <c r="B95">
         <v>0</v>
@@ -4481,13 +4193,17 @@
       <c r="H95">
         <v>0</v>
       </c>
-      <c r="I95" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>218</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Got a land title or ownership document made or corrected</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>impact_water_land_8</t>
+        </is>
       </c>
       <c r="B96">
         <v>0</v>
@@ -4510,13 +4226,17 @@
       <c r="H96">
         <v>0</v>
       </c>
-      <c r="I96" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>220</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Got access to common land that was previously blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>impact_water_land_other</t>
+        </is>
       </c>
       <c r="B97">
         <v>0</v>
@@ -4539,13 +4259,17 @@
       <c r="H97">
         <v>0</v>
       </c>
-      <c r="I97" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>221</v>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>impact_belong_1</t>
+        </is>
       </c>
       <c r="B98">
         <v>1</v>
@@ -4568,13 +4292,17 @@
       <c r="H98">
         <v>0</v>
       </c>
-      <c r="I98" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>223</v>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Feel less alone or isolated than before (have made new friends)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>impact_belong_2</t>
+        </is>
       </c>
       <c r="B99">
         <v>0</v>
@@ -4597,13 +4325,17 @@
       <c r="H99">
         <v>0</v>
       </c>
-      <c r="I99" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>225</v>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Feel that people in my community look out for each other</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>impact_belong_3</t>
+        </is>
       </c>
       <c r="B100">
         <v>0</v>
@@ -4626,13 +4358,17 @@
       <c r="H100">
         <v>0</v>
       </c>
-      <c r="I100" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>227</v>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Feel that I belong to a group that shares my struggles and values</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>impact_belong_4</t>
+        </is>
       </c>
       <c r="B101">
         <v>0</v>
@@ -4655,13 +4391,17 @@
       <c r="H101">
         <v>0</v>
       </c>
-      <c r="I101" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>229</v>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Feel more hopeful about the future because of the people around me</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>impact_belong_5</t>
+        </is>
       </c>
       <c r="B102">
         <v>0</v>
@@ -4684,13 +4424,17 @@
       <c r="H102">
         <v>0</v>
       </c>
-      <c r="I102" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>231</v>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Conflict or tension within the community has reduced</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>impact_belong_6</t>
+        </is>
       </c>
       <c r="B103">
         <v>1</v>
@@ -4713,13 +4457,17 @@
       <c r="H103">
         <v>1</v>
       </c>
-      <c r="I103" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>233</v>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>People from different castes, religions, or backgrounds are mixing more than before</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>impact_belong_other</t>
+        </is>
       </c>
       <c r="B104">
         <v>1</v>
@@ -4742,13 +4490,17 @@
       <c r="H104">
         <v>0</v>
       </c>
-      <c r="I104" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>234</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>impact_envir_1</t>
+        </is>
       </c>
       <c r="B105">
         <v>3</v>
@@ -4771,13 +4523,17 @@
       <c r="H105">
         <v>0</v>
       </c>
-      <c r="I105" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>236</v>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Participated in tree planting or forest conservation</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>impact_envir_2</t>
+        </is>
       </c>
       <c r="B106">
         <v>1</v>
@@ -4800,13 +4556,17 @@
       <c r="H106">
         <v>0</v>
       </c>
-      <c r="I106" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>238</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Helped protect a water body (e.g. river, pond, wetland)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>impact_envir_3</t>
+        </is>
       </c>
       <c r="B107">
         <v>0</v>
@@ -4829,13 +4589,17 @@
       <c r="H107">
         <v>0</v>
       </c>
-      <c r="I107" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>240</v>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Reduced use of chemical fertilisers or pesticides in farming</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>impact_envir_4</t>
+        </is>
       </c>
       <c r="B108">
         <v>0</v>
@@ -4858,13 +4622,17 @@
       <c r="H108">
         <v>0</v>
       </c>
-      <c r="I108" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>242</v>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Adopted climate-resilient farming practices</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>impact_envir_5</t>
+        </is>
       </c>
       <c r="B109">
         <v>1</v>
@@ -4887,13 +4655,17 @@
       <c r="H109">
         <v>0</v>
       </c>
-      <c r="I109" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>244</v>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Protected common land or forest from encroachment or destruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>impact_envir_6</t>
+        </is>
       </c>
       <c r="B110">
         <v>0</v>
@@ -4916,13 +4688,17 @@
       <c r="H110">
         <v>0</v>
       </c>
-      <c r="I110" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>246</v>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Community is better prepared for floods, droughts, heatwaves, other natural disasters</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>impact_envir_7</t>
+        </is>
       </c>
       <c r="B111">
         <v>0</v>
@@ -4945,13 +4721,17 @@
       <c r="H111">
         <v>0</v>
       </c>
-      <c r="I111" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>248</v>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Got support during or after a natural disaster</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>impact_envir_8</t>
+        </is>
       </c>
       <c r="B112">
         <v>0</v>
@@ -4974,13 +4754,17 @@
       <c r="H112">
         <v>0</v>
       </c>
-      <c r="I112" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>250</v>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Waste management in the village or neighbourhood has improved</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>impact_envir_9</t>
+        </is>
       </c>
       <c r="B113">
         <v>0</v>
@@ -5003,13 +4787,17 @@
       <c r="H113">
         <v>0</v>
       </c>
-      <c r="I113" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>252</v>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Air or water pollution in the area has reduced</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>impact_envir_10</t>
+        </is>
       </c>
       <c r="B114">
         <v>0</v>
@@ -5032,13 +4820,17 @@
       <c r="H114">
         <v>0</v>
       </c>
-      <c r="I114" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>254</v>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Feel better prepared for the climate crisis and its impact on future generations</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>impact_envir_other</t>
+        </is>
       </c>
       <c r="B115">
         <v>0</v>
@@ -5061,8 +4853,10 @@
       <c r="H115">
         <v>0</v>
       </c>
-      <c r="I115" t="s">
-        <v>58</v>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
       </c>
     </row>
   </sheetData>
